--- a/data/persone.xlsx
+++ b/data/persone.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140BD7D1-8CF9-49C1-9370-EBF202F56D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A38B8E5-8990-4BFB-8D8E-880D370210DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Nome</t>
   </si>
@@ -49,6 +49,9 @@
   </si>
   <si>
     <t>Roberto Sassi</t>
+  </si>
+  <si>
+    <t>193?</t>
   </si>
 </sst>
 </file>
@@ -104,8 +107,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6380CEA1-2840-445B-ADBD-7320006564D3}" name="Tabella1" displayName="Tabella1" ref="A1:C6" totalsRowShown="0">
-  <autoFilter ref="A1:C6" xr:uid="{6380CEA1-2840-445B-ADBD-7320006564D3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6380CEA1-2840-445B-ADBD-7320006564D3}" name="Tabella1" displayName="Tabella1" ref="A1:C49" totalsRowShown="0">
+  <autoFilter ref="A1:C49" xr:uid="{6380CEA1-2840-445B-ADBD-7320006564D3}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{6410E973-265C-4D04-8C0B-E2FA2C9FF53E}" name="Nome"/>
     <tableColumn id="2" xr3:uid="{7CAE0CA3-7241-43AF-9B51-02729062C91E}" name="Nascita"/>
@@ -410,20 +413,44 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
+      <c r="B3">
+        <v>1921</v>
+      </c>
+      <c r="C3">
+        <v>1993</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>2021</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
+      <c r="B5">
+        <v>1931</v>
+      </c>
+      <c r="C5">
+        <v>2005</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
+      </c>
+      <c r="B6">
+        <v>1960</v>
+      </c>
+      <c r="C6">
+        <v>2023</v>
       </c>
     </row>
   </sheetData>

--- a/data/persone.xlsx
+++ b/data/persone.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A38B8E5-8990-4BFB-8D8E-880D370210DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{848037B8-60D9-4F64-960C-FAA0720F891E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Nome</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t>193?</t>
+  </si>
+  <si>
+    <t>Vincenzo Calò</t>
   </si>
 </sst>
 </file>
@@ -381,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -453,6 +456,11 @@
         <v>2023</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/persone.xlsx
+++ b/data/persone.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{848037B8-60D9-4F64-960C-FAA0720F891E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9714CA-2239-4BAF-87BA-7D47BB54F433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Nome</t>
   </si>
@@ -55,6 +55,24 @@
   </si>
   <si>
     <t>Vincenzo Calò</t>
+  </si>
+  <si>
+    <t>Dino Dini</t>
+  </si>
+  <si>
+    <t>Lin Biao</t>
+  </si>
+  <si>
+    <t>Kang Sheng</t>
+  </si>
+  <si>
+    <t>Zhou Enlai</t>
+  </si>
+  <si>
+    <t>Chen Boda</t>
+  </si>
+  <si>
+    <t>Jiang Qing</t>
   </si>
 </sst>
 </file>
@@ -384,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -461,6 +479,36 @@
         <v>9</v>
       </c>
     </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/persone.xlsx
+++ b/data/persone.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9714CA-2239-4BAF-87BA-7D47BB54F433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17CEA7E-7032-4F93-9AEB-CA199207CCC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Nome</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>Jiang Qing</t>
+  </si>
+  <si>
+    <t>Angiolo Gracci</t>
   </si>
 </sst>
 </file>
@@ -402,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -488,25 +491,66 @@
       <c r="A9" t="s">
         <v>11</v>
       </c>
+      <c r="B9">
+        <v>1907</v>
+      </c>
+      <c r="C9">
+        <v>1971</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
+      <c r="B10">
+        <v>1898</v>
+      </c>
+      <c r="C10">
+        <v>1975</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
+      <c r="B11">
+        <v>1898</v>
+      </c>
+      <c r="C11">
+        <v>1976</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
+      <c r="B12">
+        <v>1904</v>
+      </c>
+      <c r="C12">
+        <v>1989</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>15</v>
+      </c>
+      <c r="B13">
+        <v>1914</v>
+      </c>
+      <c r="C13">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>1920</v>
+      </c>
+      <c r="C14">
+        <v>2004</v>
       </c>
     </row>
   </sheetData>

--- a/data/persone.xlsx
+++ b/data/persone.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17CEA7E-7032-4F93-9AEB-CA199207CCC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3ACE94D-DEB6-479B-9074-BA7AE8D2BA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Nome</t>
   </si>
@@ -36,46 +36,88 @@
     <t>Morte</t>
   </si>
   <si>
-    <t>Mao Zedong</t>
-  </si>
-  <si>
-    <t>Fosco Dinucci</t>
-  </si>
-  <si>
-    <t>Osvaldo Pesce</t>
-  </si>
-  <si>
-    <t>Yao Wenyuan</t>
-  </si>
-  <si>
-    <t>Roberto Sassi</t>
-  </si>
-  <si>
     <t>193?</t>
   </si>
   <si>
-    <t>Vincenzo Calò</t>
-  </si>
-  <si>
-    <t>Dino Dini</t>
-  </si>
-  <si>
-    <t>Lin Biao</t>
-  </si>
-  <si>
-    <t>Kang Sheng</t>
-  </si>
-  <si>
-    <t>Zhou Enlai</t>
-  </si>
-  <si>
-    <t>Chen Boda</t>
-  </si>
-  <si>
-    <t>Jiang Qing</t>
-  </si>
-  <si>
-    <t>Angiolo Gracci</t>
+    <t>Cognome</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Zedong</t>
+  </si>
+  <si>
+    <t>Mao</t>
+  </si>
+  <si>
+    <t>Dinucci</t>
+  </si>
+  <si>
+    <t>Pesce</t>
+  </si>
+  <si>
+    <t>Wenyuan</t>
+  </si>
+  <si>
+    <t>Sassi</t>
+  </si>
+  <si>
+    <t>Calò</t>
+  </si>
+  <si>
+    <t>Dini</t>
+  </si>
+  <si>
+    <t>Biao</t>
+  </si>
+  <si>
+    <t>Sheng</t>
+  </si>
+  <si>
+    <t>Enlai</t>
+  </si>
+  <si>
+    <t>Boda</t>
+  </si>
+  <si>
+    <t>Qing</t>
+  </si>
+  <si>
+    <t>Gracci</t>
+  </si>
+  <si>
+    <t>Fosco</t>
+  </si>
+  <si>
+    <t>Osvaldo</t>
+  </si>
+  <si>
+    <t>Yao</t>
+  </si>
+  <si>
+    <t>Roberto</t>
+  </si>
+  <si>
+    <t>Vincenzo</t>
+  </si>
+  <si>
+    <t>Dino</t>
+  </si>
+  <si>
+    <t>Lin</t>
+  </si>
+  <si>
+    <t>Kang</t>
+  </si>
+  <si>
+    <t>Zhou</t>
+  </si>
+  <si>
+    <t>Chen</t>
+  </si>
+  <si>
+    <t>Jiang</t>
+  </si>
+  <si>
+    <t>Angiolo</t>
   </si>
 </sst>
 </file>
@@ -131,10 +173,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6380CEA1-2840-445B-ADBD-7320006564D3}" name="Tabella1" displayName="Tabella1" ref="A1:C49" totalsRowShown="0">
-  <autoFilter ref="A1:C49" xr:uid="{6380CEA1-2840-445B-ADBD-7320006564D3}"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6380CEA1-2840-445B-ADBD-7320006564D3}" name="Tabella1" displayName="Tabella1" ref="A1:D49" totalsRowShown="0">
+  <autoFilter ref="A1:D49" xr:uid="{6380CEA1-2840-445B-ADBD-7320006564D3}"/>
+  <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{6410E973-265C-4D04-8C0B-E2FA2C9FF53E}" name="Nome"/>
+    <tableColumn id="4" xr3:uid="{DB3C9769-5CD0-4C0C-A8A3-68E46C171DA7}" name="Cognome"/>
     <tableColumn id="2" xr3:uid="{7CAE0CA3-7241-43AF-9B51-02729062C91E}" name="Nascita"/>
     <tableColumn id="3" xr3:uid="{68013688-5509-4E4B-A2F7-8D6DFE4E5D7B}" name="Morte"/>
   </tableColumns>
@@ -405,151 +448,193 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
         <v>1893</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>1976</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
         <v>1921</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1993</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4">
         <v>2021</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5">
         <v>1931</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>2005</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
         <v>1960</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>2023</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9">
         <v>1907</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>1971</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10">
         <v>1898</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>1975</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11">
         <v>1898</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>1976</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12">
         <v>1904</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>1989</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13">
         <v>1914</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>1991</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14">
         <v>1920</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>2004</v>
       </c>
     </row>

--- a/data/persone.xlsx
+++ b/data/persone.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3ACE94D-DEB6-479B-9074-BA7AE8D2BA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF9AD44-1DB1-4A8C-8FC4-B553A644C796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,9 +42,6 @@
     <t>Cognome</t>
   </si>
   <si>
-    <t xml:space="preserve"> Zedong</t>
-  </si>
-  <si>
     <t>Mao</t>
   </si>
   <si>
@@ -54,9 +51,6 @@
     <t>Pesce</t>
   </si>
   <si>
-    <t>Wenyuan</t>
-  </si>
-  <si>
     <t>Sassi</t>
   </si>
   <si>
@@ -66,42 +60,12 @@
     <t>Dini</t>
   </si>
   <si>
-    <t>Biao</t>
-  </si>
-  <si>
-    <t>Sheng</t>
-  </si>
-  <si>
-    <t>Enlai</t>
-  </si>
-  <si>
-    <t>Boda</t>
-  </si>
-  <si>
-    <t>Qing</t>
-  </si>
-  <si>
     <t>Gracci</t>
   </si>
   <si>
-    <t>Fosco</t>
-  </si>
-  <si>
-    <t>Osvaldo</t>
-  </si>
-  <si>
     <t>Yao</t>
   </si>
   <si>
-    <t>Roberto</t>
-  </si>
-  <si>
-    <t>Vincenzo</t>
-  </si>
-  <si>
-    <t>Dino</t>
-  </si>
-  <si>
     <t>Lin</t>
   </si>
   <si>
@@ -117,7 +81,43 @@
     <t>Jiang</t>
   </si>
   <si>
-    <t>Angiolo</t>
+    <t>Mao Zedong</t>
+  </si>
+  <si>
+    <t>Fosco Dinucci</t>
+  </si>
+  <si>
+    <t>Osvaldo Pesce</t>
+  </si>
+  <si>
+    <t>Yao Wenyuan</t>
+  </si>
+  <si>
+    <t>Roberto Sassi</t>
+  </si>
+  <si>
+    <t>Vincenzo Calò</t>
+  </si>
+  <si>
+    <t>Dino Dini</t>
+  </si>
+  <si>
+    <t>Lin Biao</t>
+  </si>
+  <si>
+    <t>Kang Sheng</t>
+  </si>
+  <si>
+    <t>Zhou Enlai</t>
+  </si>
+  <si>
+    <t>Chen Boda</t>
+  </si>
+  <si>
+    <t>Jiang Qing</t>
+  </si>
+  <si>
+    <t>Angiolo Gracci</t>
   </si>
 </sst>
 </file>
@@ -451,6 +451,7 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="18.21875" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -470,10 +471,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
       </c>
       <c r="C2">
         <v>1893</v>
@@ -487,7 +488,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>1921</v>
@@ -501,7 +502,7 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -512,10 +513,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <v>1931</v>
@@ -529,7 +530,7 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>1960</v>
@@ -543,7 +544,7 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -551,15 +552,15 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
         <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
       </c>
       <c r="C9">
         <v>1907</v>
@@ -570,10 +571,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
         <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
       </c>
       <c r="C10">
         <v>1898</v>
@@ -584,10 +585,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
         <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
       </c>
       <c r="C11">
         <v>1898</v>
@@ -598,10 +599,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
         <v>16</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
       </c>
       <c r="C12">
         <v>1904</v>
@@ -612,10 +613,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
         <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
       </c>
       <c r="C13">
         <v>1914</v>
@@ -629,7 +630,7 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C14">
         <v>1920</v>

--- a/data/persone.xlsx
+++ b/data/persone.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF9AD44-1DB1-4A8C-8FC4-B553A644C796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F29D354-90F6-4745-B108-6F44069FF7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Nome</t>
   </si>
@@ -118,6 +118,12 @@
   </si>
   <si>
     <t>Angiolo Gracci</t>
+  </si>
+  <si>
+    <t>Immagini</t>
+  </si>
+  <si>
+    <t>mao.png</t>
   </si>
 </sst>
 </file>
@@ -173,13 +179,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6380CEA1-2840-445B-ADBD-7320006564D3}" name="Tabella1" displayName="Tabella1" ref="A1:D49" totalsRowShown="0">
-  <autoFilter ref="A1:D49" xr:uid="{6380CEA1-2840-445B-ADBD-7320006564D3}"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6380CEA1-2840-445B-ADBD-7320006564D3}" name="Tabella1" displayName="Tabella1" ref="A1:E49" totalsRowShown="0">
+  <autoFilter ref="A1:E49" xr:uid="{6380CEA1-2840-445B-ADBD-7320006564D3}"/>
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{6410E973-265C-4D04-8C0B-E2FA2C9FF53E}" name="Nome"/>
     <tableColumn id="4" xr3:uid="{DB3C9769-5CD0-4C0C-A8A3-68E46C171DA7}" name="Cognome"/>
     <tableColumn id="2" xr3:uid="{7CAE0CA3-7241-43AF-9B51-02729062C91E}" name="Nascita"/>
     <tableColumn id="3" xr3:uid="{68013688-5509-4E4B-A2F7-8D6DFE4E5D7B}" name="Morte"/>
+    <tableColumn id="5" xr3:uid="{336FC867-8D07-44CD-ABD7-D557C710E149}" name="Immagini"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -448,14 +455,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.21875" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -468,8 +475,11 @@
       <c r="D1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -482,8 +492,11 @@
       <c r="D2">
         <v>1976</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -497,7 +510,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -511,7 +524,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -525,7 +538,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -539,7 +552,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -547,7 +560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -555,7 +568,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -569,7 +582,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -583,7 +596,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -597,7 +610,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -611,7 +624,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -625,7 +638,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/data/persone.xlsx
+++ b/data/persone.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F29D354-90F6-4745-B108-6F44069FF7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856DF00B-ED98-4466-9D5F-61F5961CE63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -120,10 +120,10 @@
     <t>Angiolo Gracci</t>
   </si>
   <si>
-    <t>Immagini</t>
-  </si>
-  <si>
     <t>mao.png</t>
+  </si>
+  <si>
+    <t>Immagine</t>
   </si>
 </sst>
 </file>
@@ -186,7 +186,7 @@
     <tableColumn id="4" xr3:uid="{DB3C9769-5CD0-4C0C-A8A3-68E46C171DA7}" name="Cognome"/>
     <tableColumn id="2" xr3:uid="{7CAE0CA3-7241-43AF-9B51-02729062C91E}" name="Nascita"/>
     <tableColumn id="3" xr3:uid="{68013688-5509-4E4B-A2F7-8D6DFE4E5D7B}" name="Morte"/>
-    <tableColumn id="5" xr3:uid="{336FC867-8D07-44CD-ABD7-D557C710E149}" name="Immagini"/>
+    <tableColumn id="5" xr3:uid="{336FC867-8D07-44CD-ABD7-D557C710E149}" name="Immagine"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -476,7 +476,7 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -493,7 +493,7 @@
         <v>1976</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">

--- a/data/persone.xlsx
+++ b/data/persone.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856DF00B-ED98-4466-9D5F-61F5961CE63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19F9ABE-CDFF-4DA3-9B15-BF02D598C013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Nome</t>
   </si>
@@ -124,6 +124,9 @@
   </si>
   <si>
     <t>Immagine</t>
+  </si>
+  <si>
+    <t>pesce.png</t>
   </si>
 </sst>
 </file>
@@ -523,6 +526,9 @@
       <c r="D4">
         <v>2021</v>
       </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">

--- a/data/persone.xlsx
+++ b/data/persone.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19F9ABE-CDFF-4DA3-9B15-BF02D598C013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61698A38-7E45-4A57-B1B5-74F8448CB217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -30,103 +25,103 @@
     <t>Nome</t>
   </si>
   <si>
+    <t>Cognome</t>
+  </si>
+  <si>
     <t>Nascita</t>
   </si>
   <si>
     <t>Morte</t>
   </si>
   <si>
+    <t>Immagine</t>
+  </si>
+  <si>
+    <t>Mao Zedong</t>
+  </si>
+  <si>
+    <t>Fosco Dinucci</t>
+  </si>
+  <si>
+    <t>Osvaldo Pesce</t>
+  </si>
+  <si>
+    <t>Yao Wenyuan</t>
+  </si>
+  <si>
+    <t>Roberto Sassi</t>
+  </si>
+  <si>
+    <t>Vincenzo Calò</t>
+  </si>
+  <si>
+    <t>Dino Dini</t>
+  </si>
+  <si>
+    <t>Lin Biao</t>
+  </si>
+  <si>
+    <t>Kang Sheng</t>
+  </si>
+  <si>
+    <t>Zhou Enlai</t>
+  </si>
+  <si>
+    <t>Chen Boda</t>
+  </si>
+  <si>
+    <t>Jiang Qing</t>
+  </si>
+  <si>
+    <t>Angiolo Gracci</t>
+  </si>
+  <si>
+    <t>Mao</t>
+  </si>
+  <si>
+    <t>Dinucci</t>
+  </si>
+  <si>
+    <t>Pesce</t>
+  </si>
+  <si>
+    <t>Yao</t>
+  </si>
+  <si>
+    <t>Sassi</t>
+  </si>
+  <si>
+    <t>Calò</t>
+  </si>
+  <si>
+    <t>Dini</t>
+  </si>
+  <si>
+    <t>Lin</t>
+  </si>
+  <si>
+    <t>Kang</t>
+  </si>
+  <si>
+    <t>Zhou</t>
+  </si>
+  <si>
+    <t>Chen</t>
+  </si>
+  <si>
+    <t>Jiang</t>
+  </si>
+  <si>
+    <t>Gracci</t>
+  </si>
+  <si>
     <t>193?</t>
   </si>
   <si>
-    <t>Cognome</t>
-  </si>
-  <si>
-    <t>Mao</t>
-  </si>
-  <si>
-    <t>Dinucci</t>
-  </si>
-  <si>
-    <t>Pesce</t>
-  </si>
-  <si>
-    <t>Sassi</t>
-  </si>
-  <si>
-    <t>Calò</t>
-  </si>
-  <si>
-    <t>Dini</t>
-  </si>
-  <si>
-    <t>Gracci</t>
-  </si>
-  <si>
-    <t>Yao</t>
-  </si>
-  <si>
-    <t>Lin</t>
-  </si>
-  <si>
-    <t>Kang</t>
-  </si>
-  <si>
-    <t>Zhou</t>
-  </si>
-  <si>
-    <t>Chen</t>
-  </si>
-  <si>
-    <t>Jiang</t>
-  </si>
-  <si>
-    <t>Mao Zedong</t>
-  </si>
-  <si>
-    <t>Fosco Dinucci</t>
-  </si>
-  <si>
-    <t>Osvaldo Pesce</t>
-  </si>
-  <si>
-    <t>Yao Wenyuan</t>
-  </si>
-  <si>
-    <t>Roberto Sassi</t>
-  </si>
-  <si>
-    <t>Vincenzo Calò</t>
-  </si>
-  <si>
-    <t>Dino Dini</t>
-  </si>
-  <si>
-    <t>Lin Biao</t>
-  </si>
-  <si>
-    <t>Kang Sheng</t>
-  </si>
-  <si>
-    <t>Zhou Enlai</t>
-  </si>
-  <si>
-    <t>Chen Boda</t>
-  </si>
-  <si>
-    <t>Jiang Qing</t>
-  </si>
-  <si>
-    <t>Angiolo Gracci</t>
-  </si>
-  <si>
-    <t>mao.png</t>
-  </si>
-  <si>
-    <t>Immagine</t>
-  </si>
-  <si>
-    <t>pesce.png</t>
+    <t>mao.webp</t>
+  </si>
+  <si>
+    <t>pesce.webp</t>
   </si>
 </sst>
 </file>
@@ -162,14 +157,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -182,23 +178,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6380CEA1-2840-445B-ADBD-7320006564D3}" name="Tabella1" displayName="Tabella1" ref="A1:E49" totalsRowShown="0">
-  <autoFilter ref="A1:E49" xr:uid="{6380CEA1-2840-445B-ADBD-7320006564D3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D971E570-05E9-4FFD-AB8F-DA2ADD24CB87}" name="Tabella1" displayName="Tabella1" ref="A1:E23" totalsRowShown="0">
+  <autoFilter ref="A1:E23" xr:uid="{D971E570-05E9-4FFD-AB8F-DA2ADD24CB87}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{6410E973-265C-4D04-8C0B-E2FA2C9FF53E}" name="Nome"/>
-    <tableColumn id="4" xr3:uid="{DB3C9769-5CD0-4C0C-A8A3-68E46C171DA7}" name="Cognome"/>
-    <tableColumn id="2" xr3:uid="{7CAE0CA3-7241-43AF-9B51-02729062C91E}" name="Nascita"/>
-    <tableColumn id="3" xr3:uid="{68013688-5509-4E4B-A2F7-8D6DFE4E5D7B}" name="Morte"/>
-    <tableColumn id="5" xr3:uid="{336FC867-8D07-44CD-ABD7-D557C710E149}" name="Immagine"/>
+    <tableColumn id="1" xr3:uid="{2774ABB1-9730-4A01-ABA2-CEB0185A5CE3}" name="Nome"/>
+    <tableColumn id="2" xr3:uid="{E04C5659-FEB8-410C-959C-2E08B876D94A}" name="Cognome"/>
+    <tableColumn id="3" xr3:uid="{641BC1C6-B45C-4E7B-9112-CFDE8FFAE50D}" name="Nascita"/>
+    <tableColumn id="4" xr3:uid="{57FF6F79-881D-458D-A613-B30B8D6EEA48}" name="Morte"/>
+    <tableColumn id="5" xr3:uid="{47DE922E-E83E-4D45-91ED-2708DA450227}" name="Immagine"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -206,44 +202,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -273,12 +269,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -308,7 +304,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -317,142 +313,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -461,8 +481,7 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.21875" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="1" max="5" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -470,60 +489,60 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>1893</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>1976</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>1921</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>1993</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
       <c r="C4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4">
+        <v>31</v>
+      </c>
+      <c r="D4" s="1">
         <v>2021</v>
       </c>
       <c r="E4" t="s">
@@ -532,129 +551,129 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>1931</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>2005</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
         <v>22</v>
       </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>1960</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>2023</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
         <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>1907</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>1971</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
         <v>26</v>
       </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>1898</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>1975</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
         <v>27</v>
       </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>1898</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>1976</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
         <v>28</v>
       </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>1904</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>1989</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
         <v>29</v>
       </c>
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>1914</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>1991</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
         <v>30</v>
       </c>
-      <c r="B14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>1920</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>2004</v>
       </c>
     </row>

--- a/data/persone.xlsx
+++ b/data/persone.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61698A38-7E45-4A57-B1B5-74F8448CB217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F509F15E-B69B-4098-9E08-089E18519151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Nome</t>
   </si>
@@ -122,6 +122,12 @@
   </si>
   <si>
     <t>pesce.webp</t>
+  </si>
+  <si>
+    <t>Giorgio Zucchetti</t>
+  </si>
+  <si>
+    <t>Zucchetti</t>
   </si>
 </sst>
 </file>
@@ -157,9 +163,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -478,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="5" width="10.6640625" customWidth="1"/>
@@ -508,10 +513,10 @@
       <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2">
         <v>1893</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2">
         <v>1976</v>
       </c>
       <c r="E2" t="s">
@@ -525,10 +530,10 @@
       <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <v>1921</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3">
         <v>1993</v>
       </c>
     </row>
@@ -542,7 +547,7 @@
       <c r="C4" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4">
         <v>2021</v>
       </c>
       <c r="E4" t="s">
@@ -556,10 +561,10 @@
       <c r="B5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5">
         <v>1931</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5">
         <v>2005</v>
       </c>
     </row>
@@ -570,10 +575,10 @@
       <c r="B6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6">
         <v>1960</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6">
         <v>2023</v>
       </c>
     </row>
@@ -600,10 +605,10 @@
       <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9">
         <v>1907</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9">
         <v>1971</v>
       </c>
     </row>
@@ -614,10 +619,10 @@
       <c r="B10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10">
         <v>1898</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10">
         <v>1975</v>
       </c>
     </row>
@@ -628,10 +633,10 @@
       <c r="B11" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11">
         <v>1898</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11">
         <v>1976</v>
       </c>
     </row>
@@ -642,10 +647,10 @@
       <c r="B12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12">
         <v>1904</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12">
         <v>1989</v>
       </c>
     </row>
@@ -656,10 +661,10 @@
       <c r="B13" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13">
         <v>1914</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13">
         <v>1991</v>
       </c>
     </row>
@@ -670,11 +675,25 @@
       <c r="B14" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14">
         <v>1920</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14">
         <v>2004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15">
+        <v>1920</v>
+      </c>
+      <c r="D15">
+        <v>1997</v>
       </c>
     </row>
   </sheetData>

--- a/data/persone.xlsx
+++ b/data/persone.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivan_\Desktop\AMI\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F509F15E-B69B-4098-9E08-089E18519151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4E1C09-C4C8-4177-8D00-D7E6B0706FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3516" yWindow="1248" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Nome</t>
   </si>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t>Zucchetti</t>
+  </si>
+  <si>
+    <t>dinucci.webp</t>
   </si>
 </sst>
 </file>
@@ -536,6 +539,9 @@
       <c r="D3">
         <v>1993</v>
       </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
